--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487834_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487834_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.0774</v>
+        <v>9.693199999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3096</v>
+        <v>7.1309</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7678</v>
+        <v>2.5623</v>
       </c>
       <c r="G2" t="n">
         <v>2.9352</v>
@@ -610,13 +610,13 @@
         <v>2.2893</v>
       </c>
       <c r="S2" t="n">
-        <v>2.6833</v>
+        <v>1.2991</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7731</v>
+        <v>0.5944</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9102</v>
+        <v>0.7047</v>
       </c>
       <c r="V2" t="n">
         <v>4.2102</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8135</v>
+        <v>3.5331</v>
       </c>
       <c r="E3" t="n">
-        <v>3.561</v>
+        <v>2.8109</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2525</v>
+        <v>0.7222</v>
       </c>
       <c r="G3" t="n">
         <v>1.3954</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7104</v>
+        <v>0.4301</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0464</v>
+        <v>0.2963</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.336</v>
+        <v>0.1338</v>
       </c>
       <c r="V3" t="n">
         <v>1.2914</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8351</v>
+        <v>2.5963</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0137</v>
+        <v>2.1408</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1786</v>
+        <v>0.4555</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.06</v>
+        <v>0.3708</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6037</v>
+        <v>-0.6138</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4564</v>
+        <v>0.9846</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6109</v>
+        <v>0.6242</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0251</v>
+        <v>0.2111</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.636</v>
+        <v>0.4131</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4492</v>
+        <v>-0.2533</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6288</v>
+        <v>-0.8248</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1796</v>
+        <v>0.5715</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2926</v>
+        <v>0.5606</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9971</v>
+        <v>0.3491</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2956</v>
+        <v>0.2114</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6275</v>
+        <v>1.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8574</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>M. DE PABLO DEL CASTILLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0606</v>
+        <v>1.5408</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6051</v>
+        <v>0.8753</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4555</v>
+        <v>0.6655</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3708</v>
+        <v>1.9549</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6138</v>
+        <v>0.8829</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9846</v>
+        <v>1.072</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6242</v>
+        <v>1.8244</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2111</v>
+        <v>1.324</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4131</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2533</v>
+        <v>0.1304</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8248</v>
+        <v>-0.4411</v>
       </c>
       <c r="O5" t="n">
         <v>0.5715</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6649</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q5" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="V5" t="n">
+        <v>-0.4599</v>
+      </c>
+      <c r="W5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.6649</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.0248</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-0.1866</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.2114</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.1675</v>
-      </c>
       <c r="X5" t="n">
-        <v>-1.1675</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. DE PABLO DEL CASTILLO</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7995</v>
+        <v>0.9254</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3395</v>
+        <v>2.192</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4599</v>
+        <v>-1.2666</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9549</v>
+        <v>-1.06</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8829</v>
+        <v>-0.6037</v>
       </c>
       <c r="I6" t="n">
-        <v>1.072</v>
+        <v>-0.4564</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8244</v>
+        <v>-0.6109</v>
       </c>
       <c r="K6" t="n">
-        <v>1.324</v>
+        <v>0.0251</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5004999999999999</v>
+        <v>-0.636</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1304</v>
+        <v>-0.4492</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4411</v>
+        <v>-0.6288</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5715</v>
+        <v>0.1796</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4873</v>
+        <v>1.3829</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4443</v>
+        <v>1.1754</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.043</v>
+        <v>0.2075</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.4599</v>
+        <v>-0.23</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.4599</v>
+        <v>-1.8574</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0187</v>
+        <v>-0.0495</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2433</v>
+        <v>-0.9219000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2247</v>
+        <v>0.8723</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8929</v>
@@ -1000,13 +1000,13 @@
         <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>0.458</v>
+        <v>0.4272</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0281</v>
+        <v>0.2934</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4861</v>
+        <v>0.1338</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3299</v>
+        <v>-0.164</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1043</v>
+        <v>0.0029</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2256</v>
+        <v>-0.1669</v>
       </c>
       <c r="G8" t="n">
         <v>-1.7202</v>
@@ -1078,13 +1078,13 @@
         <v>0.8325</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5578</v>
+        <v>0.7237</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3353</v>
+        <v>0.4425</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2225</v>
+        <v>0.2812</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5315</v>
+        <v>-1.9253</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7737</v>
+        <v>-0.1111</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2421</v>
+        <v>-1.8142</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2166</v>
+        <v>-0.8428</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3987</v>
+        <v>0.7035</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1821</v>
+        <v>-1.5463</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6368</v>
+        <v>0.529</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.676</v>
+        <v>2.0059</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0392</v>
+        <v>-1.4769</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5798</v>
+        <v>-1.3719</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7227</v>
+        <v>-1.3025</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1429</v>
+        <v>-0.0694</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4162</v>
+        <v>0.4162</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6851</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3262</v>
+        <v>0.1705</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0113</v>
+        <v>0.4358</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5838</v>
+        <v>-2.1051</v>
       </c>
       <c r="W9" t="n">
         <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8137</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8501</v>
+        <v>-1.9719</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1826</v>
+        <v>-1.7737</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6674</v>
+        <v>-0.1983</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8428</v>
+        <v>-1.2166</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7035</v>
+        <v>-1.3987</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5463</v>
+        <v>0.1821</v>
       </c>
       <c r="J10" t="n">
-        <v>0.529</v>
+        <v>-0.6368</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0059</v>
+        <v>-0.676</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.4769</v>
+        <v>0.0392</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3719</v>
+        <v>-0.5798</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3025</v>
+        <v>-0.7227</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0694</v>
+        <v>0.1429</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4162</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4568</v>
+        <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3184</v>
+        <v>0.2447</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.901</v>
+        <v>-0.3262</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5826</v>
+        <v>0.5709</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1051</v>
+        <v>-0.5838</v>
       </c>
       <c r="W10" t="n">
         <v>0.23</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3351</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.176</v>
+        <v>-3.6578</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6902</v>
+        <v>-4.583</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5141</v>
+        <v>0.9252</v>
       </c>
       <c r="G11" t="n">
         <v>-3.5405</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.366</v>
+        <v>0.1522</v>
       </c>
       <c r="T11" t="n">
-        <v>0.152</v>
+        <v>0.2591</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.518</v>
+        <v>-0.107</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4776</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.7022</v>
+        <v>-5.5426</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9534</v>
+        <v>-3.8818</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7488</v>
+        <v>-1.6607</v>
       </c>
       <c r="G12" t="n">
         <v>-3.1801</v>
@@ -1390,13 +1390,13 @@
         <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.749</v>
+        <v>0.4107</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0191</v>
+        <v>0.0524</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2701</v>
+        <v>0.3582</v>
       </c>
       <c r="V12" t="n">
         <v>-2.565</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.9777</v>
+        <v>4.977699999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.881399999999998</v>
+        <v>3.881300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0962</v>
+        <v>1.0963</v>
       </c>
       <c r="G13" t="n">
         <v>-5.796799999999999</v>
@@ -1441,10 +1441,10 @@
         <v>-4.1229</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9002999999999992</v>
+        <v>0.9002999999999983</v>
       </c>
       <c r="K13" t="n">
-        <v>7.533800000000001</v>
+        <v>7.533799999999999</v>
       </c>
       <c r="L13" t="n">
         <v>-6.6334</v>
@@ -1453,10 +1453,10 @@
         <v>-6.697299999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.207800000000001</v>
+        <v>-9.207799999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>2.510500000000001</v>
+        <v>2.5105</v>
       </c>
       <c r="P13" t="n">
         <v>5.2029</v>
@@ -1468,19 +1468,19 @@
         <v>13.5277</v>
       </c>
       <c r="S13" t="n">
-        <v>6.4913</v>
+        <v>6.4916</v>
       </c>
       <c r="T13" t="n">
-        <v>3.3986</v>
+        <v>3.3984</v>
       </c>
       <c r="U13" t="n">
         <v>3.0928</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9198000000000002</v>
+        <v>-0.9197999999999997</v>
       </c>
       <c r="W13" t="n">
-        <v>7.9074</v>
+        <v>7.907400000000002</v>
       </c>
       <c r="X13" t="n">
         <v>-8.8271</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7662</v>
+        <v>2.4839</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8491</v>
+        <v>2.9562</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0829</v>
+        <v>-0.4724</v>
       </c>
       <c r="G14" t="n">
         <v>2.0666</v>
@@ -1546,13 +1546,13 @@
         <v>0.4162</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0503</v>
+        <v>-0.2321</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4972</v>
+        <v>-0.39</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5475</v>
+        <v>0.1579</v>
       </c>
       <c r="V14" t="n">
         <v>1.2737</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>L. GARCIA MUÑOZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2474</v>
+        <v>0.9787</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.77</v>
+        <v>-0.3211</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0174</v>
+        <v>1.2998</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1514</v>
+        <v>2.8727</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2772</v>
+        <v>0.1001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4286</v>
+        <v>2.7726</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.4568</v>
+        <v>2.0117</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.028</v>
+        <v>0.8842</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4287</v>
+        <v>1.1275</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6082</v>
+        <v>0.861</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2492</v>
+        <v>-0.7841</v>
       </c>
       <c r="O15" t="n">
-        <v>1.8574</v>
+        <v>1.6451</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8325</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4162</v>
+        <v>-2.4974</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2487</v>
+        <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7411</v>
+        <v>-0.5839</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5806</v>
+        <v>-0.5252</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1605</v>
+        <v>-0.0586</v>
       </c>
       <c r="V15" t="n">
         <v>-0.4776</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4776</v>
+        <v>0.6899</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. STEVANIC</t>
+          <t>G. VILLAREJO COSTA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8726</v>
+        <v>0.9779</v>
       </c>
       <c r="E16" t="n">
-        <v>0.276</v>
+        <v>1.0807</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5966</v>
+        <v>-0.1028</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2062</v>
+        <v>0.4323</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3858</v>
+        <v>0.3221</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1796</v>
+        <v>0.1102</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0959</v>
+        <v>0.71</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0959</v>
+        <v>0.71</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3022</v>
+        <v>-0.2777</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4818</v>
+        <v>-0.3879</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1796</v>
+        <v>0.1102</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.6244</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4162</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.2275</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0.2414</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.3975</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.3975</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-0.2081</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.2081</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.3712</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.3882</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.0169</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.7076</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.7076</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. VILLAREJO COSTA</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4969</v>
+        <v>0.8418</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9735</v>
+        <v>-2.5201</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4766</v>
+        <v>3.3619</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4323</v>
+        <v>0.1514</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3221</v>
+        <v>-0.2772</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1102</v>
+        <v>0.4286</v>
       </c>
       <c r="J17" t="n">
-        <v>0.71</v>
+        <v>-1.4568</v>
       </c>
       <c r="K17" t="n">
-        <v>0.71</v>
+        <v>-0.028</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-1.4287</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2777</v>
+        <v>1.6082</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3879</v>
+        <v>-0.2492</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1102</v>
+        <v>1.8574</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>-0.4162</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4162</v>
+        <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7085</v>
+        <v>0.3355</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.1695</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6152</v>
+        <v>0.505</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3975</v>
+        <v>-0.4776</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3975</v>
+        <v>-0.4776</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>V. STEVANIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0294</v>
+        <v>0.6544</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7497</v>
+        <v>0.0617</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7791</v>
+        <v>0.5927</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8727</v>
+        <v>-0.2062</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1001</v>
+        <v>-0.3858</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7726</v>
+        <v>0.1796</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0117</v>
+        <v>0.0959</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8842</v>
+        <v>0.0959</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1275</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.861</v>
+        <v>-0.3022</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7841</v>
+        <v>-0.4818</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6451</v>
+        <v>0.1796</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4974</v>
+        <v>-0.2081</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6649</v>
+        <v>0.2081</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5331</v>
+        <v>0.153</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9539</v>
+        <v>0.1738</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5793</v>
+        <v>-0.0209</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4776</v>
+        <v>0.7076</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6899</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4535</v>
+        <v>-0.0963</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7865</v>
+        <v>1.0008</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.24</v>
+        <v>-1.0971</v>
       </c>
       <c r="G19" t="n">
         <v>2.8722</v>
@@ -1936,13 +1936,13 @@
         <v>1.0406</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0125</v>
+        <v>-0.6553</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7053</v>
+        <v>-0.491</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3072</v>
+        <v>-0.1643</v>
       </c>
       <c r="V19" t="n">
         <v>-2.1051</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2645</v>
+        <v>-1.2034</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7452</v>
+        <v>-2.8524</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4807</v>
+        <v>1.649</v>
       </c>
       <c r="G20" t="n">
         <v>0.342</v>
@@ -2014,13 +2014,13 @@
         <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5441</v>
+        <v>-0.4829</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4228</v>
+        <v>-0.53</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1212</v>
+        <v>0.0471</v>
       </c>
       <c r="V20" t="n">
         <v>-0.23</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6994</v>
+        <v>-2.282</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7641</v>
+        <v>-0.8713</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9353</v>
+        <v>-1.4107</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5429</v>
@@ -2092,13 +2092,13 @@
         <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.451</v>
+        <v>-1.0336</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6433</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8076</v>
+        <v>-0.2831</v>
       </c>
       <c r="V21" t="n">
         <v>2.3351</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7747</v>
+        <v>-2.3485</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5659</v>
+        <v>1.6731</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3406</v>
+        <v>-4.0215</v>
       </c>
       <c r="G22" t="n">
         <v>0.8137</v>
@@ -2170,13 +2170,13 @@
         <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4823</v>
+        <v>-1.0561</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3138</v>
+        <v>-0.2067</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1684</v>
+        <v>-0.8494</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2737</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1981</v>
+        <v>-2.8409</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5181</v>
+        <v>-1.3038</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.68</v>
+        <v>-1.5371</v>
       </c>
       <c r="G23" t="n">
         <v>-1.005</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9225</v>
+        <v>-0.5653</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4319</v>
+        <v>-0.2176</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4906</v>
+        <v>-0.3477</v>
       </c>
       <c r="V23" t="n">
         <v>-0.23</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9777</v>
+        <v>-2.8344</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0961</v>
+        <v>-1.0962</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.881600000000001</v>
+        <v>-1.738199999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>5.7968</v>
+        <v>5.796800000000001</v>
       </c>
       <c r="H24" t="n">
         <v>1.6738</v>
@@ -2323,22 +2323,22 @@
         <v>-13.5276</v>
       </c>
       <c r="R24" t="n">
-        <v>8.324499999999999</v>
+        <v>8.3245</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.491400000000001</v>
+        <v>-4.348199999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.0927</v>
+        <v>-3.0929</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.398400000000001</v>
+        <v>-1.2554</v>
       </c>
       <c r="V24" t="n">
-        <v>0.9199000000000004</v>
+        <v>0.9198999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>8.827199999999999</v>
+        <v>8.827200000000001</v>
       </c>
       <c r="X24" t="n">
         <v>-7.907400000000001</v>
